--- a/artfynd/A 13889-2024 artfynd.xlsx
+++ b/artfynd/A 13889-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6659,6 +6659,238 @@
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>118079671</v>
+      </c>
+      <c r="B54" t="n">
+        <v>94339</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Berg Stenkullen, Vg</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>339337</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6431932</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Ingela Eriksson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Ingela Eriksson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>118079630</v>
+      </c>
+      <c r="B55" t="n">
+        <v>97836</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Stenkullen mossa, Vg</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>339337</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6431951</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Ingela Eriksson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Ingela Eriksson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13889-2024 artfynd.xlsx
+++ b/artfynd/A 13889-2024 artfynd.xlsx
@@ -5786,7 +5786,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117490445</v>
+        <v>117490389</v>
       </c>
       <c r="B47" t="n">
         <v>97836</v>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5834,14 +5834,14 @@
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>stenkullen 4, Vg</t>
+          <t>Stenkullen 3, Vg</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>339322</v>
+        <v>339333</v>
       </c>
       <c r="R47" t="n">
-        <v>6431956</v>
+        <v>6431955</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5873,17 +5873,17 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
           <t>11:30</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2024-06-01</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6036,7 +6036,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117490389</v>
+        <v>117490445</v>
       </c>
       <c r="B49" t="n">
         <v>97836</v>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6084,14 +6084,14 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stenkullen 3, Vg</t>
+          <t>stenkullen 4, Vg</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>339333</v>
+        <v>339322</v>
       </c>
       <c r="R49" t="n">
-        <v>6431955</v>
+        <v>6431956</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6411,7 +6411,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117908305</v>
+        <v>117908290</v>
       </c>
       <c r="B52" t="n">
         <v>97836</v>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6459,14 +6459,14 @@
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stenkullen 9, Vg</t>
+          <t>Stenkullen 8, Vg</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>339294</v>
+        <v>339261</v>
       </c>
       <c r="R52" t="n">
-        <v>6431847</v>
+        <v>6431840</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6536,7 +6536,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117908290</v>
+        <v>117908305</v>
       </c>
       <c r="B53" t="n">
         <v>97836</v>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6584,14 +6584,14 @@
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stenkullen 8, Vg</t>
+          <t>Stenkullen 9, Vg</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>339261</v>
+        <v>339294</v>
       </c>
       <c r="R53" t="n">
-        <v>6431840</v>
+        <v>6431847</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6661,10 +6661,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118079671</v>
+        <v>118079630</v>
       </c>
       <c r="B54" t="n">
-        <v>94339</v>
+        <v>97836</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6673,42 +6673,50 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2667</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Berg Stenkullen, Vg</t>
+          <t>Stenkullen mossa, Vg</t>
         </is>
       </c>
       <c r="Q54" t="n">
         <v>339337</v>
       </c>
       <c r="R54" t="n">
-        <v>6431932</v>
+        <v>6431951</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6738,9 +6746,19 @@
           <t>2024-06-28</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6768,10 +6786,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118079630</v>
+        <v>118079671</v>
       </c>
       <c r="B55" t="n">
-        <v>97836</v>
+        <v>94339</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6780,50 +6798,42 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>2667</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stenkullen mossa, Vg</t>
+          <t>Berg Stenkullen, Vg</t>
         </is>
       </c>
       <c r="Q55" t="n">
         <v>339337</v>
       </c>
       <c r="R55" t="n">
-        <v>6431951</v>
+        <v>6431932</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6853,19 +6863,9 @@
           <t>2024-06-28</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 13889-2024 artfynd.xlsx
+++ b/artfynd/A 13889-2024 artfynd.xlsx
@@ -5786,10 +5786,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117490389</v>
+        <v>117490445</v>
       </c>
       <c r="B47" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5834,14 +5834,14 @@
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stenkullen 3, Vg</t>
+          <t>stenkullen 4, Vg</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>339333</v>
+        <v>339322</v>
       </c>
       <c r="R47" t="n">
-        <v>6431955</v>
+        <v>6431956</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5914,7 +5914,7 @@
         <v>117490501</v>
       </c>
       <c r="B48" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6036,10 +6036,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117490445</v>
+        <v>117490389</v>
       </c>
       <c r="B49" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6084,14 +6084,14 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>stenkullen 4, Vg</t>
+          <t>Stenkullen 3, Vg</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>339322</v>
+        <v>339333</v>
       </c>
       <c r="R49" t="n">
-        <v>6431956</v>
+        <v>6431955</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6123,17 +6123,17 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
           <t>11:30</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2024-06-01</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6164,7 +6164,7 @@
         <v>117604067</v>
       </c>
       <c r="B50" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>117690082</v>
       </c>
       <c r="B51" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6411,10 +6411,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117908290</v>
+        <v>117908305</v>
       </c>
       <c r="B52" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6459,14 +6459,14 @@
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stenkullen 8, Vg</t>
+          <t>Stenkullen 9, Vg</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>339261</v>
+        <v>339294</v>
       </c>
       <c r="R52" t="n">
-        <v>6431840</v>
+        <v>6431847</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6536,10 +6536,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117908305</v>
+        <v>117908290</v>
       </c>
       <c r="B53" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6584,14 +6584,14 @@
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stenkullen 9, Vg</t>
+          <t>Stenkullen 8, Vg</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>339294</v>
+        <v>339261</v>
       </c>
       <c r="R53" t="n">
-        <v>6431847</v>
+        <v>6431840</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6664,7 +6664,7 @@
         <v>118079630</v>
       </c>
       <c r="B54" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>118079671</v>
       </c>
       <c r="B55" t="n">
-        <v>94339</v>
+        <v>94341</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>

--- a/artfynd/A 13889-2024 artfynd.xlsx
+++ b/artfynd/A 13889-2024 artfynd.xlsx
@@ -8347,7 +8347,7 @@
         <v>119479519</v>
       </c>
       <c r="B68" t="n">
-        <v>91842</v>
+        <v>91860</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>

--- a/artfynd/A 13889-2024 artfynd.xlsx
+++ b/artfynd/A 13889-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3299,10 +3299,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>116722490</v>
+        <v>116722474</v>
       </c>
       <c r="B25" t="n">
-        <v>96724</v>
+        <v>94189</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3315,19 +3315,23 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221944</v>
+        <v>2810</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3335,10 +3339,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>339339</v>
+        <v>339300</v>
       </c>
       <c r="R25" t="n">
-        <v>6431900</v>
+        <v>6431901</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3379,7 +3383,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3391,17 +3394,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Amanda Tas, Anna-Karin Hellman</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>116722474</v>
+        <v>116722479</v>
       </c>
       <c r="B26" t="n">
-        <v>94189</v>
+        <v>57294</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3410,25 +3413,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3438,10 +3441,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>339300</v>
+        <v>339241</v>
       </c>
       <c r="R26" t="n">
-        <v>6431901</v>
+        <v>6431816</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3474,6 +3477,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3500,10 +3508,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>116722479</v>
+        <v>116722491</v>
       </c>
       <c r="B27" t="n">
-        <v>57294</v>
+        <v>96403</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3512,25 +3520,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3540,10 +3548,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>339241</v>
+        <v>339198</v>
       </c>
       <c r="R27" t="n">
-        <v>6431816</v>
+        <v>6431867</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3576,11 +3584,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-05-04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3607,10 +3610,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>116722491</v>
+        <v>116722480</v>
       </c>
       <c r="B28" t="n">
-        <v>96403</v>
+        <v>57294</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3619,25 +3622,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3647,10 +3650,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>339198</v>
+        <v>339348</v>
       </c>
       <c r="R28" t="n">
-        <v>6431867</v>
+        <v>6431919</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3683,6 +3686,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3709,10 +3717,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>116722480</v>
+        <v>116722487</v>
       </c>
       <c r="B29" t="n">
-        <v>57294</v>
+        <v>96730</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3721,25 +3729,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3749,10 +3757,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>339348</v>
+        <v>339300</v>
       </c>
       <c r="R29" t="n">
-        <v>6431919</v>
+        <v>6431901</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3785,11 +3793,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-05-04</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3816,10 +3819,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>116722487</v>
+        <v>117095235</v>
       </c>
       <c r="B30" t="n">
-        <v>96730</v>
+        <v>97800</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3828,41 +3831,53 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stenkullen, Vg</t>
+          <t>Ale Stenkullen 1:5, pos 7, Vg</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>339300</v>
+        <v>339314</v>
       </c>
       <c r="R30" t="n">
-        <v>6431901</v>
+        <v>6431948</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3886,12 +3901,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3900,28 +3915,29 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Anna Pielach</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Anna Pielach</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117095235</v>
+        <v>117106013</v>
       </c>
       <c r="B31" t="n">
-        <v>97800</v>
+        <v>94097</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3930,50 +3946,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>2779</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ale Stenkullen 1:5, pos 7, Vg</t>
+          <t>Ale Stenkullen 1:5, pos 9, Vg</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>339314</v>
+        <v>339278</v>
       </c>
       <c r="R31" t="n">
-        <v>6431948</v>
+        <v>6431822</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4033,10 +4041,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117106013</v>
+        <v>117093960</v>
       </c>
       <c r="B32" t="n">
-        <v>94097</v>
+        <v>102105</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4045,25 +4053,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2779</v>
+        <v>223246</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4073,14 +4081,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ale Stenkullen 1:5, pos 9, Vg</t>
+          <t>Ale Stenkullen 1:5, pos 2, Vg</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>339278</v>
+        <v>339284</v>
       </c>
       <c r="R32" t="n">
-        <v>6431822</v>
+        <v>6431918</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4140,10 +4148,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117093960</v>
+        <v>117094780</v>
       </c>
       <c r="B33" t="n">
-        <v>102105</v>
+        <v>97800</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4152,42 +4160,50 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>223246</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ale Stenkullen 1:5, pos 2, Vg</t>
+          <t>Ale Stenkullen 1:5, pos 3, Vg</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>339284</v>
+        <v>339338</v>
       </c>
       <c r="R33" t="n">
-        <v>6431918</v>
+        <v>6431949</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4247,10 +4263,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117094780</v>
+        <v>117106007</v>
       </c>
       <c r="B34" t="n">
-        <v>97800</v>
+        <v>94292</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4259,35 +4275,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -4295,14 +4311,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Ale Stenkullen 1:5, pos 3, Vg</t>
+          <t>Ale Stenkullen 1:5, pos 9, Vg</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>339338</v>
+        <v>339278</v>
       </c>
       <c r="R34" t="n">
-        <v>6431949</v>
+        <v>6431822</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4362,10 +4378,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117106007</v>
+        <v>117106026</v>
       </c>
       <c r="B35" t="n">
-        <v>94292</v>
+        <v>96428</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4378,33 +4394,25 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4477,10 +4485,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117106026</v>
+        <v>117094877</v>
       </c>
       <c r="B36" t="n">
-        <v>96428</v>
+        <v>97800</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4489,42 +4497,50 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2606</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Ale Stenkullen 1:5, pos 9, Vg</t>
+          <t>Ale Stenkullen 1:5, pos 4, Vg</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>339278</v>
+        <v>339331</v>
       </c>
       <c r="R36" t="n">
-        <v>6431822</v>
+        <v>6431939</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4584,7 +4600,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117094877</v>
+        <v>117094996</v>
       </c>
       <c r="B37" t="n">
         <v>97800</v>
@@ -4619,27 +4635,23 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Ale Stenkullen 1:5, pos 4, Vg</t>
+          <t>Ale Stenkullen 1:5, pos 5, Vg</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>339331</v>
+        <v>339330</v>
       </c>
       <c r="R37" t="n">
-        <v>6431939</v>
+        <v>6431952</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4672,6 +4684,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-05-19</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Minst 100 plantor, troligtvis fler</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4699,7 +4716,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117094996</v>
+        <v>117095165</v>
       </c>
       <c r="B38" t="n">
         <v>97800</v>
@@ -4734,23 +4751,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ale Stenkullen 1:5, pos 5, Vg</t>
+          <t>Ale Stenkullen 1:5, pos 6, Vg</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>339330</v>
+        <v>339320</v>
       </c>
       <c r="R38" t="n">
-        <v>6431952</v>
+        <v>6431948</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4783,11 +4804,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-05-19</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Minst 100 plantor, troligtvis fler</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4815,10 +4831,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117095165</v>
+        <v>117093838</v>
       </c>
       <c r="B39" t="n">
-        <v>97800</v>
+        <v>74548</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4827,50 +4843,49 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Ale Stenkullen 1:5, pos 6, Vg</t>
+          <t>Ale Stenkullen 1:5, Vg</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>339320</v>
+        <v>339197</v>
       </c>
       <c r="R39" t="n">
-        <v>6431948</v>
+        <v>6431861</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4914,6 +4929,31 @@
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4930,10 +4970,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117093838</v>
+        <v>117091222</v>
       </c>
       <c r="B40" t="n">
-        <v>74548</v>
+        <v>57959</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4946,48 +4986,49 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>308</v>
+        <v>103055</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>cm²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ale Stenkullen 1:5, Vg</t>
+          <t>Stenkullen, Risveden, Vg</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>339197</v>
+        <v>339214</v>
       </c>
       <c r="R40" t="n">
-        <v>6431861</v>
+        <v>6431907</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5014,65 +5055,49 @@
           <t>2024-05-19</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-05-19</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Blandsumpskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anna Pielach</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anna Pielach</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117091222</v>
+        <v>117106029</v>
       </c>
       <c r="B41" t="n">
-        <v>57959</v>
+        <v>100061</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5081,53 +5106,45 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103055</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stenkullen, Risveden, Vg</t>
+          <t>Ale Stenkullen 1:5, pos 9, Vg</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>339214</v>
+        <v>339278</v>
       </c>
       <c r="R41" t="n">
-        <v>6431907</v>
+        <v>6431822</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5154,49 +5171,40 @@
           <t>2024-05-19</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-05-19</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Anna Pielach</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Anna Pielach</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117106029</v>
+        <v>117106019</v>
       </c>
       <c r="B42" t="n">
-        <v>100061</v>
+        <v>94088</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5209,21 +5217,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>2755</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skuggsprötmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Eurhynchium striatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5300,54 +5308,66 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117106019</v>
+        <v>117103022</v>
       </c>
       <c r="B43" t="n">
-        <v>94088</v>
+        <v>96524</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2755</v>
+        <v>2617</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skuggsprötmossa</t>
+          <t>Flikbålmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Eurhynchium striatum</t>
+          <t>Riccardia multifida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ale Stenkullen 1:5, pos 9, Vg</t>
+          <t>Ale Stenkullen 1:5, pos 8, Vg</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>339278</v>
+        <v>339319</v>
       </c>
       <c r="R43" t="n">
-        <v>6431822</v>
+        <v>6431916</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5407,10 +5427,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117103022</v>
+        <v>117094007</v>
       </c>
       <c r="B44" t="n">
-        <v>96524</v>
+        <v>94303</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5419,30 +5439,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2617</v>
+        <v>2667</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Flikbålmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Riccardia multifida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5450,23 +5470,19 @@
           <t>dm²</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ale Stenkullen 1:5, pos 8, Vg</t>
+          <t>Ale Stenkullen 1:5, pos 2, Vg</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>339319</v>
+        <v>339284</v>
       </c>
       <c r="R44" t="n">
-        <v>6431916</v>
+        <v>6431918</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5510,6 +5526,21 @@
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5526,47 +5557,47 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117094007</v>
+        <v>117426000</v>
       </c>
       <c r="B45" t="n">
-        <v>94303</v>
+        <v>97836</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2667</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -5574,14 +5605,14 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Ale Stenkullen 1:5, pos 2, Vg</t>
+          <t>Stenkullen, Vg</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>339284</v>
+        <v>339324</v>
       </c>
       <c r="R45" t="n">
-        <v>6431918</v>
+        <v>6431956</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5608,12 +5639,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Cirka 27 plantor spridda över ett område på cirka 2 x 0,4 meter.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5626,40 +5672,25 @@
       <c r="AG45" t="b">
         <v>0</v>
       </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anna Pielach</t>
+          <t>Ingela Eriksson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna Pielach</t>
+          <t>Ingela Eriksson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117426000</v>
+        <v>117490445</v>
       </c>
       <c r="B46" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5691,7 +5722,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5704,17 +5735,17 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stenkullen, Vg</t>
+          <t>stenkullen 4, Vg</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>339324</v>
+        <v>339322</v>
       </c>
       <c r="R46" t="n">
         <v>6431956</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5738,27 +5769,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Cirka 27 plantor spridda över ett område på cirka 2 x 0,4 meter.</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5786,7 +5812,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117490445</v>
+        <v>117490501</v>
       </c>
       <c r="B47" t="n">
         <v>97838</v>
@@ -5821,7 +5847,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>94</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5834,14 +5860,14 @@
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>stenkullen 4, Vg</t>
+          <t>stenkullen 5, Vg</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>339322</v>
+        <v>339342</v>
       </c>
       <c r="R47" t="n">
-        <v>6431956</v>
+        <v>6431949</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5911,7 +5937,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117490501</v>
+        <v>117490389</v>
       </c>
       <c r="B48" t="n">
         <v>97838</v>
@@ -5946,7 +5972,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5959,14 +5985,14 @@
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>stenkullen 5, Vg</t>
+          <t>Stenkullen 3, Vg</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>339342</v>
+        <v>339333</v>
       </c>
       <c r="R48" t="n">
-        <v>6431949</v>
+        <v>6431955</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5998,17 +6024,17 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
           <t>11:30</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2024-06-01</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6036,7 +6062,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117490389</v>
+        <v>117604067</v>
       </c>
       <c r="B49" t="n">
         <v>97838</v>
@@ -6071,7 +6097,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6084,17 +6110,17 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stenkullen 3, Vg</t>
+          <t>Stenkullen branten, Vg</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>339333</v>
+        <v>339189</v>
       </c>
       <c r="R49" t="n">
-        <v>6431955</v>
+        <v>6431823</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6118,22 +6144,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6161,7 +6187,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117604067</v>
+        <v>117690082</v>
       </c>
       <c r="B50" t="n">
         <v>97838</v>
@@ -6196,7 +6222,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6209,14 +6235,14 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stenkullen branten, Vg</t>
+          <t>Stenkullen 6, Vg</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>339189</v>
+        <v>339208</v>
       </c>
       <c r="R50" t="n">
-        <v>6431823</v>
+        <v>6431824</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6243,22 +6269,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6286,10 +6312,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117690082</v>
+        <v>117908305</v>
       </c>
       <c r="B51" t="n">
-        <v>97838</v>
+        <v>97840</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6321,7 +6347,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6334,14 +6360,14 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stenkullen 6, Vg</t>
+          <t>Stenkullen 9, Vg</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>339208</v>
+        <v>339294</v>
       </c>
       <c r="R51" t="n">
-        <v>6431824</v>
+        <v>6431847</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6368,22 +6394,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6411,7 +6437,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117908305</v>
+        <v>117908290</v>
       </c>
       <c r="B52" t="n">
         <v>97840</v>
@@ -6446,7 +6472,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6459,14 +6485,14 @@
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stenkullen 9, Vg</t>
+          <t>Stenkullen 8, Vg</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>339294</v>
+        <v>339261</v>
       </c>
       <c r="R52" t="n">
-        <v>6431847</v>
+        <v>6431840</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6498,7 +6524,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6508,7 +6534,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6536,10 +6562,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117908290</v>
+        <v>118079671</v>
       </c>
       <c r="B53" t="n">
-        <v>97840</v>
+        <v>94349</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6548,50 +6574,42 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>2667</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stenkullen 8, Vg</t>
+          <t>Berg Stenkullen, Vg</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>339261</v>
+        <v>339337</v>
       </c>
       <c r="R53" t="n">
-        <v>6431840</v>
+        <v>6431932</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6618,22 +6636,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>16:21</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>16:21</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6661,10 +6669,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118079671</v>
+        <v>118079630</v>
       </c>
       <c r="B54" t="n">
-        <v>94349</v>
+        <v>97846</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6673,42 +6681,50 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2667</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Berg Stenkullen, Vg</t>
+          <t>Stenkullen mossa, Vg</t>
         </is>
       </c>
       <c r="Q54" t="n">
         <v>339337</v>
       </c>
       <c r="R54" t="n">
-        <v>6431932</v>
+        <v>6431951</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6738,9 +6754,19 @@
           <t>2024-06-28</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6768,7 +6794,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118079630</v>
+        <v>118285081</v>
       </c>
       <c r="B55" t="n">
         <v>97846</v>
@@ -6803,7 +6829,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6816,14 +6842,14 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stenkullen mossa, Vg</t>
+          <t>Stenkullen ny, Vg</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>339337</v>
+        <v>339262</v>
       </c>
       <c r="R55" t="n">
-        <v>6431951</v>
+        <v>6431838</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6850,22 +6876,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6893,10 +6919,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118285081</v>
+        <v>119249837</v>
       </c>
       <c r="B56" t="n">
-        <v>97846</v>
+        <v>97907</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6928,7 +6954,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6941,14 +6967,14 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stenkullen ny, Vg</t>
+          <t>Stenkullen kulle, Vg</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>339262</v>
+        <v>339304</v>
       </c>
       <c r="R56" t="n">
-        <v>6431838</v>
+        <v>6431864</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6975,22 +7001,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7006,19 +7032,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119249837</v>
+        <v>119249743</v>
       </c>
       <c r="B57" t="n">
         <v>97907</v>
@@ -7053,7 +7079,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7066,14 +7092,14 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stenkullen kulle, Vg</t>
+          <t>Stenkullen, Vg</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>339304</v>
+        <v>339334</v>
       </c>
       <c r="R57" t="n">
-        <v>6431864</v>
+        <v>6431938</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7143,7 +7169,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119249743</v>
+        <v>119249871</v>
       </c>
       <c r="B58" t="n">
         <v>97907</v>
@@ -7178,7 +7204,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7191,14 +7217,14 @@
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stenkullen, Vg</t>
+          <t>Stenkullen 10, Vg</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>339334</v>
+        <v>339280</v>
       </c>
       <c r="R58" t="n">
-        <v>6431938</v>
+        <v>6431851</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7230,7 +7256,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7240,7 +7266,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7268,7 +7294,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119249871</v>
+        <v>119357029</v>
       </c>
       <c r="B59" t="n">
         <v>97907</v>
@@ -7303,7 +7329,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7316,14 +7342,14 @@
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stenkullen 10, Vg</t>
+          <t>Stenkullen 1:5, Vg</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>339280</v>
+        <v>339207</v>
       </c>
       <c r="R59" t="n">
-        <v>6431851</v>
+        <v>6431830</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7350,22 +7376,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Uppskattningsvis ca 150 rosetter inom några kvadratmeter yta. Ev ännu fler.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7381,19 +7402,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119357029</v>
+        <v>119356917</v>
       </c>
       <c r="B60" t="n">
         <v>97907</v>
@@ -7428,7 +7449,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7445,7 +7466,7 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>339207</v>
+        <v>339185</v>
       </c>
       <c r="R60" t="n">
         <v>6431830</v>
@@ -7485,7 +7506,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Uppskattningsvis ca 150 rosetter inom några kvadratmeter yta. Ev ännu fler.</t>
+          <t>Två rosetter och ett med blomskott.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7513,10 +7534,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119356917</v>
+        <v>119357398</v>
       </c>
       <c r="B61" t="n">
-        <v>97907</v>
+        <v>90334</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7525,39 +7546,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7565,10 +7585,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>339185</v>
+        <v>339350</v>
       </c>
       <c r="R61" t="n">
-        <v>6431830</v>
+        <v>6431915</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7605,7 +7625,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Två rosetter och ett med blomskott.</t>
+          <t>Några f k. I kanten av kärr.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7633,7 +7653,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119357398</v>
+        <v>119357662</v>
       </c>
       <c r="B62" t="n">
         <v>90334</v>
@@ -7666,16 +7686,8 @@
           <t>(Fr.) Fr.</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
@@ -7684,10 +7696,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>339350</v>
+        <v>339360</v>
       </c>
       <c r="R62" t="n">
-        <v>6431915</v>
+        <v>6431914</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7724,7 +7736,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Några f k. I kanten av kärr.</t>
+          <t>Mycket. I sumpskog.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7752,7 +7764,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119357662</v>
+        <v>119357470</v>
       </c>
       <c r="B63" t="n">
         <v>90334</v>
@@ -7785,8 +7797,16 @@
           <t>(Fr.) Fr.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
@@ -7798,7 +7818,7 @@
         <v>339360</v>
       </c>
       <c r="R63" t="n">
-        <v>6431914</v>
+        <v>6431935</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7835,7 +7855,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Mycket. I sumpskog.</t>
+          <t>Mindre bestånd, 1 mycel troligen.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7863,7 +7883,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119357470</v>
+        <v>119356781</v>
       </c>
       <c r="B64" t="n">
         <v>90334</v>
@@ -7914,10 +7934,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>339360</v>
+        <v>339192</v>
       </c>
       <c r="R64" t="n">
-        <v>6431935</v>
+        <v>6431868</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7954,7 +7974,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Mindre bestånd, 1 mycel troligen.</t>
+          <t>Några f k. Vid sumpskog.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7982,7 +8002,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119356781</v>
+        <v>119357501</v>
       </c>
       <c r="B65" t="n">
         <v>90334</v>
@@ -8033,10 +8053,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>339192</v>
+        <v>339377</v>
       </c>
       <c r="R65" t="n">
-        <v>6431868</v>
+        <v>6431925</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8073,7 +8093,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Några f k. Vid sumpskog.</t>
+          <t>Några f k. Vid en långsträckt sumpskog.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8101,10 +8121,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119357501</v>
+        <v>119357212</v>
       </c>
       <c r="B66" t="n">
-        <v>90334</v>
+        <v>97907</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8113,38 +8133,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8152,10 +8177,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>339377</v>
+        <v>339220</v>
       </c>
       <c r="R66" t="n">
-        <v>6431925</v>
+        <v>6431830</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8192,7 +8217,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Några f k. Vid en långsträckt sumpskog.</t>
+          <t>Ca 25 rosetter samlat och en blomstängel. Fortfarande blommande.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8220,66 +8245,61 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119357212</v>
+        <v>119479519</v>
       </c>
       <c r="B67" t="n">
-        <v>97907</v>
+        <v>91860</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>788</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stenkullen 1:5, Vg</t>
+          <t>Stenkullen klippa, Vg</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>339220</v>
+        <v>339216</v>
       </c>
       <c r="R67" t="n">
-        <v>6431830</v>
+        <v>6431855</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8306,17 +8326,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ca 25 rosetter samlat och en blomstängel. Fortfarande blommande.</t>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8332,139 +8357,15 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ingela Eriksson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ingela Eriksson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>119479519</v>
-      </c>
-      <c r="B68" t="n">
-        <v>91860</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>788</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Gul taggsvamp</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Hydnellum geogenium</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Stenkullen klippa, Vg</t>
-        </is>
-      </c>
-      <c r="Q68" t="n">
-        <v>339216</v>
-      </c>
-      <c r="R68" t="n">
-        <v>6431855</v>
-      </c>
-      <c r="S68" t="n">
-        <v>5</v>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Ale</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>Skepplanda</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>2024-08-31</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>2024-08-31</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AD68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF68" t="inlineStr"/>
-      <c r="AG68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT68" t="inlineStr"/>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>Ingela Eriksson</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>Ingela Eriksson</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13889-2024 artfynd.xlsx
+++ b/artfynd/A 13889-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8367,6 +8367,378 @@
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>125111047</v>
+      </c>
+      <c r="B68" t="n">
+        <v>106461</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>219686</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Vätteros</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Lathraea squamaria</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Stenkullen, Vg</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>339303</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6431917</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ca 30 blomstänglar. Har börjat blomma. Hassel, tall och gran intill.</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>125110936</v>
+      </c>
+      <c r="B69" t="n">
+        <v>106461</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>219686</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Vätteros</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lathraea squamaria</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Stenkullen, Vg</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>339305</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6431925</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ca 40 blomstänglar inom ca 2 kvm. Hassel, asp och gran intill.</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>125110773</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57883</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Stenkullen, Vg</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>339285</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6431890</v>
+      </c>
+      <c r="S70" t="n">
+        <v>25</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13889-2024 artfynd.xlsx
+++ b/artfynd/A 13889-2024 artfynd.xlsx
@@ -8369,10 +8369,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125111047</v>
+        <v>125110773</v>
       </c>
       <c r="B68" t="n">
-        <v>106461</v>
+        <v>57883</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8385,39 +8385,35 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219686</v>
+        <v>103015</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8425,13 +8421,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>339303</v>
+        <v>339285</v>
       </c>
       <c r="R68" t="n">
-        <v>6431917</v>
+        <v>6431890</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8458,14 +8454,19 @@
           <t>2025-04-20</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ca 30 blomstänglar. Har börjat blomma. Hassel, tall och gran intill.</t>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8474,7 +8475,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8493,7 +8493,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125110936</v>
+        <v>125111047</v>
       </c>
       <c r="B69" t="n">
         <v>106461</v>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8549,10 +8549,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>339305</v>
+        <v>339303</v>
       </c>
       <c r="R69" t="n">
-        <v>6431925</v>
+        <v>6431917</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8589,7 +8589,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ca 40 blomstänglar inom ca 2 kvm. Hassel, asp och gran intill.</t>
+          <t>Ca 30 blomstänglar. Har börjat blomma. Hassel, tall och gran intill.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8617,10 +8617,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125110773</v>
+        <v>125110936</v>
       </c>
       <c r="B70" t="n">
-        <v>57883</v>
+        <v>106461</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8633,35 +8633,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103015</v>
+        <v>219686</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8669,13 +8673,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>339285</v>
+        <v>339305</v>
       </c>
       <c r="R70" t="n">
-        <v>6431890</v>
+        <v>6431925</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8702,19 +8706,14 @@
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>18:00</t>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ca 40 blomstänglar inom ca 2 kvm. Hassel, asp och gran intill.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8723,6 +8722,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13889-2024 artfynd.xlsx
+++ b/artfynd/A 13889-2024 artfynd.xlsx
@@ -8369,10 +8369,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125110773</v>
+        <v>125111047</v>
       </c>
       <c r="B68" t="n">
-        <v>57883</v>
+        <v>106461</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8385,35 +8385,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103015</v>
+        <v>219686</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8421,13 +8425,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>339285</v>
+        <v>339303</v>
       </c>
       <c r="R68" t="n">
-        <v>6431890</v>
+        <v>6431917</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8454,19 +8458,14 @@
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>18:00</t>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ca 30 blomstänglar. Har börjat blomma. Hassel, tall och gran intill.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8475,6 +8474,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8493,10 +8493,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125111047</v>
+        <v>125110773</v>
       </c>
       <c r="B69" t="n">
-        <v>106461</v>
+        <v>57883</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8509,39 +8509,35 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219686</v>
+        <v>103015</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8549,13 +8545,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>339303</v>
+        <v>339285</v>
       </c>
       <c r="R69" t="n">
-        <v>6431917</v>
+        <v>6431890</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8582,14 +8578,19 @@
           <t>2025-04-20</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ca 30 blomstänglar. Har börjat blomma. Hassel, tall och gran intill.</t>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8598,7 +8599,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13889-2024 artfynd.xlsx
+++ b/artfynd/A 13889-2024 artfynd.xlsx
@@ -8369,10 +8369,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125111047</v>
+        <v>125110773</v>
       </c>
       <c r="B68" t="n">
-        <v>106461</v>
+        <v>57883</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8385,39 +8385,35 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219686</v>
+        <v>103015</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8425,13 +8421,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>339303</v>
+        <v>339285</v>
       </c>
       <c r="R68" t="n">
-        <v>6431917</v>
+        <v>6431890</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8458,14 +8454,19 @@
           <t>2025-04-20</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ca 30 blomstänglar. Har börjat blomma. Hassel, tall och gran intill.</t>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8474,7 +8475,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8493,10 +8493,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125110773</v>
+        <v>125111047</v>
       </c>
       <c r="B69" t="n">
-        <v>57883</v>
+        <v>106461</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8509,35 +8509,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103015</v>
+        <v>219686</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8545,13 +8549,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>339285</v>
+        <v>339303</v>
       </c>
       <c r="R69" t="n">
-        <v>6431890</v>
+        <v>6431917</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8578,19 +8582,14 @@
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>18:00</t>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ca 30 blomstänglar. Har börjat blomma. Hassel, tall och gran intill.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8599,6 +8598,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13889-2024 artfynd.xlsx
+++ b/artfynd/A 13889-2024 artfynd.xlsx
@@ -8369,10 +8369,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125110773</v>
+        <v>125110936</v>
       </c>
       <c r="B68" t="n">
-        <v>57883</v>
+        <v>106461</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8385,35 +8385,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103015</v>
+        <v>219686</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8421,13 +8425,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>339285</v>
+        <v>339305</v>
       </c>
       <c r="R68" t="n">
-        <v>6431890</v>
+        <v>6431925</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8454,19 +8458,14 @@
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>18:00</t>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ca 40 blomstänglar inom ca 2 kvm. Hassel, asp och gran intill.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8475,6 +8474,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8493,10 +8493,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125111047</v>
+        <v>125110773</v>
       </c>
       <c r="B69" t="n">
-        <v>106461</v>
+        <v>57883</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8509,39 +8509,35 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219686</v>
+        <v>103015</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8549,13 +8545,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>339303</v>
+        <v>339285</v>
       </c>
       <c r="R69" t="n">
-        <v>6431917</v>
+        <v>6431890</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8582,14 +8578,19 @@
           <t>2025-04-20</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ca 30 blomstänglar. Har börjat blomma. Hassel, tall och gran intill.</t>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8598,7 +8599,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8617,7 +8617,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125110936</v>
+        <v>125111047</v>
       </c>
       <c r="B70" t="n">
         <v>106461</v>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8673,10 +8673,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>339305</v>
+        <v>339303</v>
       </c>
       <c r="R70" t="n">
-        <v>6431925</v>
+        <v>6431917</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8713,7 +8713,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ca 40 blomstänglar inom ca 2 kvm. Hassel, asp och gran intill.</t>
+          <t>Ca 30 blomstänglar. Har börjat blomma. Hassel, tall och gran intill.</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 13889-2024 artfynd.xlsx
+++ b/artfynd/A 13889-2024 artfynd.xlsx
@@ -8493,10 +8493,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125110773</v>
+        <v>125111047</v>
       </c>
       <c r="B69" t="n">
-        <v>57883</v>
+        <v>106461</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8509,35 +8509,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103015</v>
+        <v>219686</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8545,13 +8549,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>339285</v>
+        <v>339303</v>
       </c>
       <c r="R69" t="n">
-        <v>6431890</v>
+        <v>6431917</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8578,19 +8582,14 @@
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>18:00</t>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ca 30 blomstänglar. Har börjat blomma. Hassel, tall och gran intill.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8599,6 +8598,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8617,10 +8617,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125111047</v>
+        <v>125110773</v>
       </c>
       <c r="B70" t="n">
-        <v>106461</v>
+        <v>57883</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8633,39 +8633,35 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219686</v>
+        <v>103015</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8673,13 +8669,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>339303</v>
+        <v>339285</v>
       </c>
       <c r="R70" t="n">
-        <v>6431917</v>
+        <v>6431890</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8706,14 +8702,19 @@
           <t>2025-04-20</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ca 30 blomstänglar. Har börjat blomma. Hassel, tall och gran intill.</t>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8722,7 +8723,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13889-2024 artfynd.xlsx
+++ b/artfynd/A 13889-2024 artfynd.xlsx
@@ -8369,10 +8369,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125110936</v>
+        <v>125110773</v>
       </c>
       <c r="B68" t="n">
-        <v>106461</v>
+        <v>57883</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8385,39 +8385,35 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219686</v>
+        <v>103015</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8425,13 +8421,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>339305</v>
+        <v>339285</v>
       </c>
       <c r="R68" t="n">
-        <v>6431925</v>
+        <v>6431890</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8458,14 +8454,19 @@
           <t>2025-04-20</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ca 40 blomstänglar inom ca 2 kvm. Hassel, asp och gran intill.</t>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8474,7 +8475,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8617,10 +8617,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125110773</v>
+        <v>125110936</v>
       </c>
       <c r="B70" t="n">
-        <v>57883</v>
+        <v>106461</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8633,35 +8633,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103015</v>
+        <v>219686</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8669,13 +8673,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>339285</v>
+        <v>339305</v>
       </c>
       <c r="R70" t="n">
-        <v>6431890</v>
+        <v>6431925</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8702,19 +8706,14 @@
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>18:00</t>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ca 40 blomstänglar inom ca 2 kvm. Hassel, asp och gran intill.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8723,6 +8722,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13889-2024 artfynd.xlsx
+++ b/artfynd/A 13889-2024 artfynd.xlsx
@@ -8369,10 +8369,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125111047</v>
+        <v>125110773</v>
       </c>
       <c r="B68" t="n">
-        <v>106461</v>
+        <v>58001</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8385,39 +8385,35 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219686</v>
+        <v>103015</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8425,13 +8421,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>339303</v>
+        <v>339285</v>
       </c>
       <c r="R68" t="n">
-        <v>6431917</v>
+        <v>6431890</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8458,14 +8454,19 @@
           <t>2025-04-20</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ca 30 blomstänglar. Har börjat blomma. Hassel, tall och gran intill.</t>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8474,7 +8475,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8493,10 +8493,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125110773</v>
+        <v>125111047</v>
       </c>
       <c r="B69" t="n">
-        <v>57883</v>
+        <v>106640</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8509,35 +8509,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103015</v>
+        <v>219686</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8545,13 +8549,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>339285</v>
+        <v>339303</v>
       </c>
       <c r="R69" t="n">
-        <v>6431890</v>
+        <v>6431917</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8578,19 +8582,14 @@
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-04-20</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>18:00</t>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ca 30 blomstänglar. Har börjat blomma. Hassel, tall och gran intill.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8599,6 +8598,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8620,7 +8620,7 @@
         <v>125110936</v>
       </c>
       <c r="B70" t="n">
-        <v>106461</v>
+        <v>106640</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>

--- a/artfynd/A 13889-2024 artfynd.xlsx
+++ b/artfynd/A 13889-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8724,6 +8724,368 @@
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>126326769</v>
+      </c>
+      <c r="B71" t="n">
+        <v>58025</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Stenkullen, Vg</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>339215</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6431815</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>126326772</v>
+      </c>
+      <c r="B72" t="n">
+        <v>58331</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Stenkullen, Vg</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>339215</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6431815</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>126326680</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57938</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Stenkullen, Vg</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>339208</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6431857</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Rörde sig efter en stund ca 100 m åt nordväst.</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13889-2024 artfynd.xlsx
+++ b/artfynd/A 13889-2024 artfynd.xlsx
@@ -8726,10 +8726,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126326769</v>
+        <v>126326772</v>
       </c>
       <c r="B71" t="n">
-        <v>58025</v>
+        <v>58331</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8737,16 +8737,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8845,10 +8845,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126326772</v>
+        <v>126326769</v>
       </c>
       <c r="B72" t="n">
-        <v>58331</v>
+        <v>58025</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8856,16 +8856,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">

--- a/artfynd/A 13889-2024 artfynd.xlsx
+++ b/artfynd/A 13889-2024 artfynd.xlsx
@@ -8726,10 +8726,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126326772</v>
+        <v>126326769</v>
       </c>
       <c r="B71" t="n">
-        <v>58331</v>
+        <v>58025</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8737,16 +8737,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8845,10 +8845,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126326769</v>
+        <v>126326772</v>
       </c>
       <c r="B72" t="n">
-        <v>58025</v>
+        <v>58331</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8856,16 +8856,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">

--- a/artfynd/A 13889-2024 artfynd.xlsx
+++ b/artfynd/A 13889-2024 artfynd.xlsx
@@ -8729,7 +8729,7 @@
         <v>126326772</v>
       </c>
       <c r="B71" t="n">
-        <v>58331</v>
+        <v>58334</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>126326769</v>
       </c>
       <c r="B72" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>126326680</v>
       </c>
       <c r="B73" t="n">
-        <v>57938</v>
+        <v>57939</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 13889-2024 artfynd.xlsx
+++ b/artfynd/A 13889-2024 artfynd.xlsx
@@ -8726,10 +8726,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126326772</v>
+        <v>126326769</v>
       </c>
       <c r="B71" t="n">
-        <v>58334</v>
+        <v>58027</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8737,16 +8737,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8845,10 +8845,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126326769</v>
+        <v>126326772</v>
       </c>
       <c r="B72" t="n">
-        <v>58027</v>
+        <v>58334</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8856,16 +8856,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">

--- a/artfynd/A 13889-2024 artfynd.xlsx
+++ b/artfynd/A 13889-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AY75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9086,6 +9086,230 @@
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>127292240</v>
+      </c>
+      <c r="B74" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Stenkullen, Risveden, Vg</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>339221</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6431894</v>
+      </c>
+      <c r="S74" t="n">
+        <v>25</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>127292913</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Stenkullen, Risveden, Vg</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>339348</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6431909</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13889-2024 artfynd.xlsx
+++ b/artfynd/A 13889-2024 artfynd.xlsx
@@ -9091,7 +9091,7 @@
         <v>127292240</v>
       </c>
       <c r="B74" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>127292913</v>
       </c>
       <c r="B75" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 13889-2024 artfynd.xlsx
+++ b/artfynd/A 13889-2024 artfynd.xlsx
@@ -9091,7 +9091,7 @@
         <v>127292240</v>
       </c>
       <c r="B74" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>127292913</v>
       </c>
       <c r="B75" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 13889-2024 artfynd.xlsx
+++ b/artfynd/A 13889-2024 artfynd.xlsx
@@ -9091,7 +9091,7 @@
         <v>127292240</v>
       </c>
       <c r="B74" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>127292913</v>
       </c>
       <c r="B75" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 13889-2024 artfynd.xlsx
+++ b/artfynd/A 13889-2024 artfynd.xlsx
@@ -9091,7 +9091,7 @@
         <v>127292240</v>
       </c>
       <c r="B74" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>127292913</v>
       </c>
       <c r="B75" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 13889-2024 artfynd.xlsx
+++ b/artfynd/A 13889-2024 artfynd.xlsx
@@ -9091,7 +9091,7 @@
         <v>127292240</v>
       </c>
       <c r="B74" t="n">
-        <v>57669</v>
+        <v>57654</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>127292913</v>
       </c>
       <c r="B75" t="n">
-        <v>57669</v>
+        <v>57654</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 13889-2024 artfynd.xlsx
+++ b/artfynd/A 13889-2024 artfynd.xlsx
@@ -9091,7 +9091,7 @@
         <v>127292240</v>
       </c>
       <c r="B74" t="n">
-        <v>57654</v>
+        <v>57669</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>127292913</v>
       </c>
       <c r="B75" t="n">
-        <v>57654</v>
+        <v>57669</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
